--- a/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_pan_minilm_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_pan_minilm_zeroshot.xlsx
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6027646998842148</v>
+        <v>0.6027646998842147</v>
       </c>
     </row>
     <row r="5">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.909244034999574</v>
+        <v>14.7631465279992</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002092981320143579</v>
+        <v>0.01062096872517928</v>
       </c>
     </row>
   </sheetData>
